--- a/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A86712-06EB-4D83-8FC2-1BDB6C746CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54207649-C074-4A93-8077-0E1541FF4159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Medio de orientación</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Personas atendidas (enero - diciembre 2025)</t>
+  </si>
+  <si>
+    <t>Personas atendidas (enero - abril 2026)</t>
   </si>
 </sst>
 </file>
@@ -137,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -145,6 +148,15 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -362,42 +374,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1001"/>
+  <dimension ref="A1:H1001"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5" customWidth="1"/>
-    <col min="3" max="3" width="39.5" customWidth="1"/>
-    <col min="4" max="4" width="37.5" customWidth="1"/>
-    <col min="5" max="6" width="38.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.8984375" customWidth="1"/>
-    <col min="8" max="26" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" customWidth="1"/>
+    <col min="4" max="4" width="17.3984375" customWidth="1"/>
+    <col min="5" max="5" width="17.296875" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="19.8984375" customWidth="1"/>
+    <col min="9" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="H1" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -419,8 +436,11 @@
       <c r="G2" s="2">
         <v>2752</v>
       </c>
+      <c r="H2">
+        <v>738</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -442,8 +462,11 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -465,8 +488,11 @@
       <c r="G4" s="1">
         <v>255</v>
       </c>
+      <c r="H4">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -488,8 +514,11 @@
       <c r="G5" s="1">
         <v>654</v>
       </c>
+      <c r="H5">
+        <v>148</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -512,19 +541,22 @@
       <c r="G6" s="2">
         <v>3663</v>
       </c>
+      <c r="H6">
+        <v>917</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
